--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,120 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127590204</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90762</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kilaön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>376289</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6565995</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid myrstack.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Janson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Janson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103419</v>
+        <v>103424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103419</v>
+        <v>103424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1025,6 +1025,373 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127628216</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103424</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>706</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svedjenäva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kilaön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>376112</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6565807</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>huggen mark på kulle</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127628162</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103424</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>706</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svedjenäva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kilaön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>376064</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6565876</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En jätteplanta och två mindre.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>traktorspår på huggen mark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127628083</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1885</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Klockgentiana</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gentiana pneumonanthe</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kilaön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>376192</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6566527</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hittades vid delvis gräsbevuxna hällar. Bete av gås och sedan i år kor. Gick runt hela ön och denna spillra var vad vi hittade. Ön har huggits på gran och kor betar. För hoppningsvis kan klockgentianan komma tillbaka.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gåsbetad häll</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103424</v>
+        <v>103425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103424</v>
+        <v>103425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103424</v>
+        <v>103425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103424</v>
+        <v>103425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105636</v>
+        <v>105638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103425</v>
+        <v>103427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103425</v>
+        <v>103427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127590204</v>
       </c>
       <c r="B4" t="n">
-        <v>90762</v>
+        <v>90764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103425</v>
+        <v>103427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103425</v>
+        <v>103427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105638</v>
+        <v>105640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
+          <t>Jan-Anders Aronson, Gunnar Flygh, Tomas Janson, Pär Dahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan-Anders Aronson, Gunnar Flygh, Tomas Janson, Pär Dahlström</t>
+          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103427</v>
+        <v>103433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103427</v>
+        <v>103433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127590204</v>
       </c>
       <c r="B4" t="n">
-        <v>90764</v>
+        <v>90770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103427</v>
+        <v>103433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103427</v>
+        <v>103433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105640</v>
+        <v>105646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103433</v>
+        <v>103436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103433</v>
+        <v>103436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127590204</v>
       </c>
       <c r="B4" t="n">
-        <v>90770</v>
+        <v>90773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103433</v>
+        <v>103436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103433</v>
+        <v>103436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105646</v>
+        <v>105649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103436</v>
+        <v>103444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103436</v>
+        <v>103444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127590204</v>
       </c>
       <c r="B4" t="n">
-        <v>90773</v>
+        <v>90781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103436</v>
+        <v>103444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103436</v>
+        <v>103444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105649</v>
+        <v>105657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
+          <t>Jan-Anders Aronson, Gunnar Flygh, Tomas Janson, Pär Dahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103444</v>
+        <v>103445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103444</v>
+        <v>103445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127590204</v>
       </c>
       <c r="B4" t="n">
-        <v>90781</v>
+        <v>90782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103444</v>
+        <v>103445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103444</v>
+        <v>103445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105657</v>
+        <v>105658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan-Anders Aronson, Gunnar Flygh, Tomas Janson, Pär Dahlström</t>
+          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103445</v>
+        <v>103446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103445</v>
+        <v>103446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127590204</v>
       </c>
       <c r="B4" t="n">
-        <v>90782</v>
+        <v>90783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103445</v>
+        <v>103446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103445</v>
+        <v>103446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105658</v>
+        <v>105659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127421182</v>
       </c>
       <c r="B2" t="n">
-        <v>103446</v>
+        <v>103447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127421166</v>
       </c>
       <c r="B3" t="n">
-        <v>103446</v>
+        <v>103447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127590204</v>
       </c>
       <c r="B4" t="n">
-        <v>90783</v>
+        <v>90784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103446</v>
+        <v>103447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127628162</v>
       </c>
       <c r="B6" t="n">
-        <v>103446</v>
+        <v>103447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127628083</v>
       </c>
       <c r="B7" t="n">
-        <v>105659</v>
+        <v>105660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>133880973</v>
       </c>
       <c r="B8" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127421182</v>
+        <v>127421166</v>
       </c>
       <c r="B2" t="n">
-        <v>103447</v>
+        <v>104160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376111</v>
+        <v>376060</v>
       </c>
       <c r="R2" t="n">
-        <v>6565831</v>
+        <v>6565904</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Nytt trakthygge.</t>
+          <t>En steril. Nytt trakthygge.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127421166</v>
+        <v>127421182</v>
       </c>
       <c r="B3" t="n">
-        <v>103447</v>
+        <v>104160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376060</v>
+        <v>376111</v>
       </c>
       <c r="R3" t="n">
-        <v>6565904</v>
+        <v>6565831</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En steril. Nytt trakthygge.</t>
+          <t>Nytt trakthygge.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,45 +913,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127590204</v>
+        <v>127628162</v>
       </c>
       <c r="B4" t="n">
-        <v>90784</v>
+        <v>104160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>706</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376289</v>
+        <v>376064</v>
       </c>
       <c r="R4" t="n">
-        <v>6565995</v>
+        <v>6565876</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,17 +994,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid myrstack.</t>
+          <t>En jätteplanta och två mindre.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,15 +1017,20 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>traktorspår på huggen mark</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Janson</t>
+          <t>Pär Dahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Janson</t>
+          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1030,7 +1040,7 @@
         <v>127628216</v>
       </c>
       <c r="B5" t="n">
-        <v>103447</v>
+        <v>104160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,27 +1156,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127628162</v>
+        <v>127628083</v>
       </c>
       <c r="B6" t="n">
-        <v>103447</v>
+        <v>106401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>706</v>
+        <v>1885</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Klockgentiana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Gentiana pneumonanthe</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1197,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376064</v>
+        <v>376192</v>
       </c>
       <c r="R6" t="n">
-        <v>6565876</v>
+        <v>6566527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1247,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En jätteplanta och två mindre.</t>
+          <t>Hittades vid delvis gräsbevuxna hällar. Bete av gås och sedan i år kor. Gick runt hela ön och denna spillra var vad vi hittade. Ön har huggits på gran och kor betar. För hoppningsvis kan klockgentianan komma tillbaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,7 +1262,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>traktorspår på huggen mark</t>
+          <t>Gåsbetad häll</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,50 +1280,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127628083</v>
+        <v>127590204</v>
       </c>
       <c r="B7" t="n">
-        <v>105660</v>
+        <v>91330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1885</v>
+        <v>4189</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klockgentiana</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gentiana pneumonanthe</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376192</v>
+        <v>376289</v>
       </c>
       <c r="R7" t="n">
-        <v>6566527</v>
+        <v>6565995</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,17 +1356,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hittades vid delvis gräsbevuxna hällar. Bete av gås och sedan i år kor. Gick runt hela ön och denna spillra var vad vi hittade. Ön har huggits på gran och kor betar. För hoppningsvis kan klockgentianan komma tillbaka.</t>
+          <t>Vid myrstack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,20 +1379,15 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Gåsbetad häll</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
+          <t>Tomas Janson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Dahlström, Tomas Janson, Gunnar Flygh, Jan-Anders Aronson</t>
+          <t>Tomas Janson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
         <v>133880973</v>
       </c>
       <c r="B8" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50956-2022 artfynd.xlsx
+++ b/artfynd/A 50956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127421182</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127628162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127628216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127628083</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1391,6 +1421,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127590204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1510,8 +1545,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133880973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>